--- a/data/trans_orig/P15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39992</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67682</t>
+          <t>69347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>33030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60296</t>
+          <t>60314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93694</t>
+          <t>95123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426382</t>
+          <t>424717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454072</t>
+          <t>453105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432635</t>
+          <t>434459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>452585</t>
+          <t>452736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>867859</t>
+          <t>866430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>901257</t>
+          <t>901239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>49721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80106</t>
+          <t>80856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49133</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82579</t>
+          <t>81466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655383</t>
+          <t>654633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685777</t>
+          <t>685768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>576361</t>
+          <t>576584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>601626</t>
+          <t>600773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1278403</t>
+          <t>1279516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>33912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60341</t>
+          <t>60640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50683</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82937</t>
+          <t>83738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>578327</t>
+          <t>578028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>605335</t>
+          <t>604756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659332</t>
+          <t>659308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676733</t>
+          <t>677291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1245475</t>
+          <t>1244674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1277729</t>
+          <t>1276965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56738</t>
+          <t>55885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30203</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46638</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77913</t>
+          <t>78087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>462409</t>
+          <t>463262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488743</t>
+          <t>488985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>485439</t>
+          <t>484348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>503127</t>
+          <t>503405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>956876</t>
+          <t>956702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>988151</t>
+          <t>989156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50458</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357805</t>
+          <t>358104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375100</t>
+          <t>375075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376835</t>
+          <t>376153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393103</t>
+          <t>393070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>740238</t>
+          <t>740156</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>765066</t>
+          <t>764810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36082</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49303</t>
+          <t>47591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274095</t>
+          <t>274538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286643</t>
+          <t>286337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306852</t>
+          <t>306544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326120</t>
+          <t>325430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586214</t>
+          <t>587926</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>608613</t>
+          <t>609802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>46557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>32069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56998</t>
+          <t>59818</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193202</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205277</t>
+          <t>205371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>286629</t>
+          <t>287351</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310308</t>
+          <t>311135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>486793</t>
+          <t>483973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>512602</t>
+          <t>511722</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>213412</t>
+          <t>212290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>272920</t>
+          <t>275280</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206321</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>379017</t>
+          <t>381713</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>461354</t>
+          <t>466311</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3003623</t>
+          <t>3001263</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3063131</t>
+          <t>3064253</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3172876</t>
+          <t>3174671</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3228116</t>
+          <t>3227204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6194387</t>
+          <t>6189430</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6276724</t>
+          <t>6274028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47035</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75906</t>
+          <t>75220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74185</t>
+          <t>74775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111542</t>
+          <t>108498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378240</t>
+          <t>378926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407111</t>
+          <t>407702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386547</t>
+          <t>386559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>408572</t>
+          <t>408532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772834</t>
+          <t>775878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>810191</t>
+          <t>809601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65754</t>
+          <t>65461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100184</t>
+          <t>100658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54332</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102016</t>
+          <t>101933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143740</t>
+          <t>145594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>586903</t>
+          <t>586429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>621333</t>
+          <t>621626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555923</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>581269</t>
+          <t>581180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1153602</t>
+          <t>1151748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1195326</t>
+          <t>1195409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42941</t>
+          <t>42177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73735</t>
+          <t>74176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41545</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69247</t>
+          <t>69513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105796</t>
+          <t>107299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608128</t>
+          <t>607687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638922</t>
+          <t>639686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669305</t>
+          <t>669030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690459</t>
+          <t>690664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286916</t>
+          <t>1285413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323465</t>
+          <t>1323199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27114</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50033</t>
+          <t>50008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57234</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90934</t>
+          <t>93202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562430</t>
+          <t>562838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>587503</t>
+          <t>587999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566166</t>
+          <t>566191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>590734</t>
+          <t>591815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139882</t>
+          <t>1137614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1173582</t>
+          <t>1174396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29791</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>40697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70114</t>
+          <t>70469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407459</t>
+          <t>407270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422061</t>
+          <t>422134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392166</t>
+          <t>392937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418009</t>
+          <t>418431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>807115</t>
+          <t>806760</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>837031</t>
+          <t>836532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30594</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>58089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282889</t>
+          <t>283012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300349</t>
+          <t>299739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317912</t>
+          <t>318753</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337410</t>
+          <t>337400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607156</t>
+          <t>605693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633188</t>
+          <t>632463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32564</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>41315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69120</t>
+          <t>69702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62128</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94151</t>
+          <t>93015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217287</t>
+          <t>217586</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236383</t>
+          <t>235388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319859</t>
+          <t>319277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347988</t>
+          <t>347664</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>544679</t>
+          <t>545815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>576702</t>
+          <t>578795</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>254257</t>
+          <t>255444</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>323070</t>
+          <t>320308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226504</t>
+          <t>230061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>294681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>498305</t>
+          <t>494687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>592513</t>
+          <t>591726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3103709</t>
+          <t>3106471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3172522</t>
+          <t>3171335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3268031</t>
+          <t>3263628</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3331805</t>
+          <t>3328248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6392575</t>
+          <t>6393362</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6486783</t>
+          <t>6490401</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>31832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57768</t>
+          <t>58065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49317</t>
+          <t>47899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79384</t>
+          <t>78387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361695</t>
+          <t>361398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387233</t>
+          <t>387631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>367603</t>
+          <t>368071</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384279</t>
+          <t>384353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735834</t>
+          <t>736831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765901</t>
+          <t>767319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64643</t>
+          <t>66531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32470</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58215</t>
+          <t>59466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90515</t>
+          <t>91256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>525853</t>
+          <t>523965</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>552009</t>
+          <t>551845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>531074</t>
+          <t>530656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>548720</t>
+          <t>548350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1063525</t>
+          <t>1062784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1095825</t>
+          <t>1094574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50149</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,47 +7392,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25048</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16511</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>37975</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25048</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>16452</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>37750</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46314</t>
+          <t>45981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78260</t>
+          <t>79762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618948</t>
+          <t>619906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643765</t>
+          <t>644417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,47 +7505,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>636338</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>623411</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>644875</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>96,21%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>636338</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>623636</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>644934</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252223</t>
+          <t>1250721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1284169</t>
+          <t>1284502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41237</t>
+          <t>41487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36688</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>39782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69400</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604811</t>
+          <t>604561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>626912</t>
+          <t>627687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>612389</t>
+          <t>611661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633300</t>
+          <t>633476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1225725</t>
+          <t>1226021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1255103</t>
+          <t>1255343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>19783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>42400</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454841</t>
+          <t>455164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470238</t>
+          <t>470182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452240</t>
+          <t>454449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>476648</t>
+          <t>477066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>913468</t>
+          <t>915709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>942164</t>
+          <t>942999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40463</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54774</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315508</t>
+          <t>315679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328742</t>
+          <t>328746</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337299</t>
+          <t>336761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358156</t>
+          <t>357555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>657318</t>
+          <t>655940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>682663</t>
+          <t>682986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>57076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73091</t>
+          <t>73584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233545</t>
+          <t>233754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248017</t>
+          <t>247926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343925</t>
+          <t>343093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371650</t>
+          <t>371178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>584076</t>
+          <t>583583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>614803</t>
+          <t>615261</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>172348</t>
+          <t>174325</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227456</t>
+          <t>228532</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166967</t>
+          <t>163810</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219653</t>
+          <t>219660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354579</t>
+          <t>355480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>431587</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3166894</t>
+          <t>3165818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3222002</t>
+          <t>3220025</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3324889</t>
+          <t>3324882</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3377575</t>
+          <t>3380732</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6507305</t>
+          <t>6508794</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6584313</t>
+          <t>6583412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63586</t>
+          <t>62839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>358014</t>
+          <t>360277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391316</t>
+          <t>391728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277824</t>
+          <t>277715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303465</t>
+          <t>303124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>649601</t>
+          <t>650348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690515</t>
+          <t>689430</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62217</t>
+          <t>60733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>379510</t>
+          <t>381105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407568</t>
+          <t>407193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486921</t>
+          <t>486783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504316</t>
+          <t>504112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>872834</t>
+          <t>874318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>906301</t>
+          <t>908157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>26146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50590</t>
+          <t>50917</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50064</t>
+          <t>50208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79950</t>
+          <t>80219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485748</t>
+          <t>485421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509422</t>
+          <t>510192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505451</t>
+          <t>503245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>522197</t>
+          <t>521672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>998856</t>
+          <t>998587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1028742</t>
+          <t>1028598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76189</t>
+          <t>77552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50020</t>
+          <t>45352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103880</t>
+          <t>103219</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>811597</t>
+          <t>810234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867699</t>
+          <t>866516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674135</t>
+          <t>674648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691526</t>
+          <t>691586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1496787</t>
+          <t>1497448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1550647</t>
+          <t>1555315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>39795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>26954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>45714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51825</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78914</t>
+          <t>79556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>520069</t>
+          <t>521439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>541412</t>
+          <t>540804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>502872</t>
+          <t>502191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520409</t>
+          <t>520951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1030225</t>
+          <t>1029583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1057314</t>
+          <t>1058291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23234</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54131</t>
+          <t>54127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67875</t>
+          <t>66138</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>344931</t>
+          <t>344408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>357849</t>
+          <t>357132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>554237</t>
+          <t>554241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>594289</t>
+          <t>594593</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>908658</t>
+          <t>910395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950422</t>
+          <t>950824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>43360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>62846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62867</t>
+          <t>62330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84872</t>
+          <t>85939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254948</t>
+          <t>253800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268030</t>
+          <t>267433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>363039</t>
+          <t>362985</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>381770</t>
+          <t>382471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>623718</t>
+          <t>622651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>645723</t>
+          <t>646260</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156189</t>
+          <t>153650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>236555</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177727</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248580</t>
+          <t>242043</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>354667</t>
+          <t>352614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>462516</t>
+          <t>461129</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3222022</t>
+          <t>3223262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3303628</t>
+          <t>3306167</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3413577</t>
+          <t>3420114</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3484430</t>
+          <t>3489316</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6659458</t>
+          <t>6660845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6767307</t>
+          <t>6769360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69347</t>
+          <t>68270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95123</t>
+          <t>92954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424717</t>
+          <t>425794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453105</t>
+          <t>454034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>434459</t>
+          <t>434891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>452736</t>
+          <t>452882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866430</t>
+          <t>868599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>901239</t>
+          <t>900861</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80856</t>
+          <t>80501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48910</t>
+          <t>49526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81466</t>
+          <t>79301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120713</t>
+          <t>119406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654633</t>
+          <t>654988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685768</t>
+          <t>685420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>576584</t>
+          <t>575968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600773</t>
+          <t>600378</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1240269</t>
+          <t>1241576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1279516</t>
+          <t>1281681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>61962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>30557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51447</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83738</t>
+          <t>84028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>578028</t>
+          <t>576706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>604756</t>
+          <t>605267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659308</t>
+          <t>659187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>677291</t>
+          <t>677316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1244674</t>
+          <t>1244384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1276965</t>
+          <t>1276654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>29985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55885</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>30067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78087</t>
+          <t>79035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>463262</t>
+          <t>463068</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488985</t>
+          <t>489162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484348</t>
+          <t>485575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>503405</t>
+          <t>503944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>956702</t>
+          <t>955754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>989156</t>
+          <t>987879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>29167</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27833</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>26589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50540</t>
+          <t>49853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>358104</t>
+          <t>357543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375075</t>
+          <t>374784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376153</t>
+          <t>376402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393070</t>
+          <t>393117</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>740156</t>
+          <t>740843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>764810</t>
+          <t>764107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47591</t>
+          <t>48681</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274538</t>
+          <t>274763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286337</t>
+          <t>287035</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306544</t>
+          <t>306160</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325430</t>
+          <t>325078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>587926</t>
+          <t>586836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609802</t>
+          <t>609626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>24089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>47499</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59818</t>
+          <t>57547</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193771</t>
+          <t>193531</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205371</t>
+          <t>206156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287351</t>
+          <t>286409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311135</t>
+          <t>309819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>483973</t>
+          <t>486244</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>511722</t>
+          <t>512788</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>212290</t>
+          <t>215378</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>275280</t>
+          <t>275818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>151737</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>203313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>381713</t>
+          <t>376930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>466311</t>
+          <t>462125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3001263</t>
+          <t>3000725</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3064253</t>
+          <t>3061165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3174671</t>
+          <t>3175884</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3227204</t>
+          <t>3227460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6189430</t>
+          <t>6193616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6274028</t>
+          <t>6278811</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46444</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75220</t>
+          <t>74574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74775</t>
+          <t>73559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108498</t>
+          <t>108659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378926</t>
+          <t>379572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407702</t>
+          <t>407898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386559</t>
+          <t>386768</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>408532</t>
+          <t>408529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>775878</t>
+          <t>775717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>809601</t>
+          <t>810817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65461</t>
+          <t>66851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100658</t>
+          <t>100936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>53719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101933</t>
+          <t>100862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145594</t>
+          <t>143886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>586429</t>
+          <t>586151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>621626</t>
+          <t>620236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556785</t>
+          <t>556536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>581180</t>
+          <t>582375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1151748</t>
+          <t>1153456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1195409</t>
+          <t>1196480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42177</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74176</t>
+          <t>74348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69513</t>
+          <t>66916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107299</t>
+          <t>105622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607687</t>
+          <t>607515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639686</t>
+          <t>639505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669030</t>
+          <t>670337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690664</t>
+          <t>690925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1285413</t>
+          <t>1287090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323199</t>
+          <t>1325796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>49211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>56947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93202</t>
+          <t>92091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562838</t>
+          <t>562861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>587999</t>
+          <t>588048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566191</t>
+          <t>566988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>591815</t>
+          <t>591143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1137614</t>
+          <t>1138725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1174396</t>
+          <t>1173869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40697</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70469</t>
+          <t>70188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>407270</t>
+          <t>407619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422134</t>
+          <t>422854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392937</t>
+          <t>393461</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418431</t>
+          <t>418112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>806760</t>
+          <t>807041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>836532</t>
+          <t>834965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31319</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>56438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283012</t>
+          <t>281895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>299739</t>
+          <t>299118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318753</t>
+          <t>317515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337400</t>
+          <t>336544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>605693</t>
+          <t>607344</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>632463</t>
+          <t>632370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>41563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>69888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>61898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93015</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>217586</t>
+          <t>216749</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235388</t>
+          <t>235455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>319277</t>
+          <t>319091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>347416</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>545815</t>
+          <t>543996</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578795</t>
+          <t>576932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>255444</t>
+          <t>253974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>320308</t>
+          <t>325624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>230061</t>
+          <t>225598</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>294681</t>
+          <t>290532</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>494687</t>
+          <t>499453</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>591726</t>
+          <t>596415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3106471</t>
+          <t>3101155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3171335</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3263628</t>
+          <t>3267777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3328248</t>
+          <t>3332711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6393362</t>
+          <t>6388673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6490401</t>
+          <t>6485635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58065</t>
+          <t>58274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27684</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47899</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78387</t>
+          <t>78988</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361398</t>
+          <t>361189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387631</t>
+          <t>387640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368071</t>
+          <t>368164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384353</t>
+          <t>384389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736831</t>
+          <t>736230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767319</t>
+          <t>767870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66531</t>
+          <t>63988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59466</t>
+          <t>58335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91256</t>
+          <t>90103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>523965</t>
+          <t>526508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>551845</t>
+          <t>552010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>530656</t>
+          <t>529836</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>548350</t>
+          <t>548569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1062784</t>
+          <t>1063937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1094574</t>
+          <t>1095705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24680</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49191</t>
+          <t>49130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37975</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45981</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79762</t>
+          <t>78685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619906</t>
+          <t>619967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644417</t>
+          <t>644309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623411</t>
+          <t>624221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>644875</t>
+          <t>645033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1250721</t>
+          <t>1251798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1284502</t>
+          <t>1284446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41487</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>35514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>69499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604561</t>
+          <t>604301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>627687</t>
+          <t>626537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>611661</t>
+          <t>613563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633476</t>
+          <t>633646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1226021</t>
+          <t>1225626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1255343</t>
+          <t>1255076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>45111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455164</t>
+          <t>454874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470182</t>
+          <t>470536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>454449</t>
+          <t>451738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>477066</t>
+          <t>476128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>915709</t>
+          <t>914992</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>942999</t>
+          <t>942750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56152</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>315679</t>
+          <t>316152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328746</t>
+          <t>328800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336761</t>
+          <t>335174</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>357555</t>
+          <t>357641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>655940</t>
+          <t>658452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>682986</t>
+          <t>683256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28991</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57076</t>
+          <t>58479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41906</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73584</t>
+          <t>73244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233754</t>
+          <t>233610</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247926</t>
+          <t>247294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343093</t>
+          <t>341690</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371178</t>
+          <t>372012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583583</t>
+          <t>583923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>615261</t>
+          <t>615388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174325</t>
+          <t>171341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>228532</t>
+          <t>229041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163810</t>
+          <t>165479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219660</t>
+          <t>222649</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>355480</t>
+          <t>353845</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>430098</t>
+          <t>430711</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3165818</t>
+          <t>3165309</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3220025</t>
+          <t>3223009</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3324882</t>
+          <t>3321893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3380732</t>
+          <t>3379063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6508794</t>
+          <t>6508181</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6583412</t>
+          <t>6585047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39710</t>
+          <t>41033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35485</t>
+          <t>40375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>25448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62839</t>
+          <t>66494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>380850</t>
+          <t>387096</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360277</t>
+          <t>366760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391728</t>
+          <t>397721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>293272</t>
+          <t>339920</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277715</t>
+          <t>322137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303124</t>
+          <t>351451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>674122</t>
+          <t>727016</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>650348</t>
+          <t>703811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689430</t>
+          <t>744857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>54007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60733</t>
+          <t>69424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>396280</t>
+          <t>443694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381105</t>
+          <t>422883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407193</t>
+          <t>456718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496530</t>
+          <t>485746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486783</t>
+          <t>476775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504112</t>
+          <t>492569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>892811</t>
+          <t>929440</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>874318</t>
+          <t>908549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908157</t>
+          <t>943399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,102 +10351,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50917</t>
+          <t>53850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>30468</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21759</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>38611</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>69016</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>54885</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>85715</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>6,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28034</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20796</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39223</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>65037</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>50208</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>80219</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10464,102 +10464,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>499336</t>
+          <t>582288</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485421</t>
+          <t>566987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510192</t>
+          <t>593176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>591671</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>583528</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>600380</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1173960</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1157261</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1188091</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>93,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>514434</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>503245</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>521672</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,83%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1013769</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>998587</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1028598</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50698</t>
+          <t>55935</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21270</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77552</t>
+          <t>73091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>42917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45352</t>
+          <t>71864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103219</t>
+          <t>108016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>837088</t>
+          <t>644682</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>810234</t>
+          <t>627526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>866516</t>
+          <t>659311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>683496</t>
+          <t>704269</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674648</t>
+          <t>693969</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691586</t>
+          <t>711539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1520584</t>
+          <t>1348952</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1497448</t>
+          <t>1329488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1555315</t>
+          <t>1365640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>95,0%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39795</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45714</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>57102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79556</t>
+          <t>84925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>532301</t>
+          <t>577850</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>521439</t>
+          <t>565583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>540804</t>
+          <t>587218</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>512516</t>
+          <t>570551</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>502191</t>
+          <t>560435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>520951</t>
+          <t>578862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1044818</t>
+          <t>1148402</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1029583</t>
+          <t>1133277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1058291</t>
+          <t>1161100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>26095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>43907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66138</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>351880</t>
+          <t>388943</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>380985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>357132</t>
+          <t>395275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>575424</t>
+          <t>402957</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>554241</t>
+          <t>393924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>594593</t>
+          <t>410690</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>927303</t>
+          <t>791900</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>910395</t>
+          <t>779758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950824</t>
+          <t>802339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>30907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43360</t>
+          <t>46905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62846</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62330</t>
+          <t>67816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85939</t>
+          <t>93835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>262022</t>
+          <t>287185</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253800</t>
+          <t>279291</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>294164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>372882</t>
+          <t>407955</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>362985</t>
+          <t>397018</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382471</t>
+          <t>417704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>634904</t>
+          <t>695140</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>622651</t>
+          <t>680972</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>646260</t>
+          <t>706991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153650</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>236555</t>
+          <t>255818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172841</t>
+          <t>207634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>242043</t>
+          <t>261005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>352614</t>
+          <t>414681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>461129</t>
+          <t>500325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3259758</t>
+          <t>3311739</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3223262</t>
+          <t>3276944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3306167</t>
+          <t>3342357</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3448554</t>
+          <t>3503071</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3420114</t>
+          <t>3474246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3489316</t>
+          <t>3527617</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6708312</t>
+          <t>6814810</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6660845</t>
+          <t>6767688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6769360</t>
+          <t>6853332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
